--- a/docs/rayo-attendance-sample.xlsx
+++ b/docs/rayo-attendance-sample.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>09:55:12</t>
+          <t>08:25:12</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -545,11 +545,11 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>10:00:05</t>
+          <t>08:29:51</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -580,11 +580,11 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10:02:51</t>
+          <t>08:30:05</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10:10:44</t>
+          <t>08:40:44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16:00:09</t>
+          <t>15:00:09</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -685,11 +685,11 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>سارا محمدی</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -699,12 +699,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16:00:31</t>
+          <t>16:28:03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -720,11 +720,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>علی رضایی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16:05:40</t>
+          <t>16:30:11</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -755,11 +755,11 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>سارا محمدی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17:58:03</t>
+          <t>17:02:30</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -790,11 +790,11 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18:01:11</t>
+          <t>17:30:31</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -825,11 +825,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>علی رضایی</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18:05:30</t>
+          <t>17:35:40</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -860,11 +860,11 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>01:45:17</t>
+          <t>00:20:02</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -895,11 +895,11 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>01:50:02</t>
+          <t>00:30:17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -930,11 +930,11 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>سارا محمدی</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>02:05:49</t>
+          <t>00:32:22</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -965,11 +965,11 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>سارا محمدی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>02:10:22</t>
+          <t>00:35:49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1000,11 +1000,11 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>09:58:40</t>
+          <t>09:00:12</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1035,11 +1035,11 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10:00:12</t>
+          <t>09:00:40</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10:20:33</t>
+          <t>09:05:33</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1105,11 +1105,11 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>امیر جعفری</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18:00:27</t>
+          <t>16:40:04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1140,11 +1140,11 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>امیر جعفری</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18:10:04</t>
+          <t>18:00:27</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1175,11 +1175,11 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>امیر جعفری</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>01:30:19</t>
+          <t>00:30:08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1210,11 +1210,11 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>سارا محمدی</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>02:00:08</t>
+          <t>00:30:15</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1245,11 +1245,11 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>سارا محمدی</t>
+          <t>امیر جعفری</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>02:00:15</t>
+          <t>00:30:19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>02:00:50</t>
+          <t>00:30:50</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10:00:02</t>
+          <t>09:00:02</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10:00:18</t>
+          <t>09:00:18</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10:00:29</t>
+          <t>09:00:29</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11:30:41</t>
+          <t>09:20:41</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1455,11 +1455,11 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16:00:03</t>
+          <t>15:00:07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1490,11 +1490,11 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16:00:07</t>
+          <t>16:00:45</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1525,11 +1525,11 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>امیر جعفری</t>
+          <t>سارا محمدی</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16:00:16</t>
+          <t>16:30:36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1560,11 +1560,11 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>علی رضایی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>16:00:21</t>
+          <t>17:00:52</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1595,11 +1595,11 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>16:00:45</t>
+          <t>17:30:03</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1630,11 +1630,11 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>امیر جعفری</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>16:01:10</t>
+          <t>17:30:16</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1665,11 +1665,11 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>سارا محمدی</t>
+          <t>علی رضایی</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>18:00:36</t>
+          <t>17:30:21</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1700,11 +1700,11 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>18:00:52</t>
+          <t>17:31:10</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>02:00:13</t>
+          <t>00:30:13</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1770,11 +1770,11 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>علی رضایی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>10:00:09</t>
+          <t>09:00:11</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1805,11 +1805,11 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10:00:11</t>
+          <t>09:00:47</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1840,11 +1840,11 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>علی رضایی</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10:00:47</t>
+          <t>09:14:09</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>13:30:58</t>
+          <t>13:00:58</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1910,11 +1910,11 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>علی رضایی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>14:30:55</t>
+          <t>14:00:04</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -1945,11 +1945,11 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>15:00:04</t>
+          <t>15:00:20</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1980,11 +1980,11 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>16:00:20</t>
+          <t>16:00:25</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2015,11 +2015,11 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>مریم حسینی</t>
+          <t>علی رضایی</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>16:00:37</t>
+          <t>16:00:55</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2050,11 +2050,11 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>سارا محمدی</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>17:00:25</t>
+          <t>16:30:14</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2085,11 +2085,11 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>سارا محمدی</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>18:00:14</t>
+          <t>17:30:37</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>19:00:06</t>
+          <t>18:00:06</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2155,11 +2155,11 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>01:00:42</t>
+          <t>00:30:31</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2190,11 +2190,11 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>02:00:31</t>
+          <t>00:30:42</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>03:15:38</t>
+          <t>01:30:38</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10:00:26</t>
+          <t>09:00:26</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>10:00:33</t>
+          <t>09:00:33</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2365,11 +2365,11 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>رضا کریمی</t>
+          <t>سارا محمدی</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>16:00:28</t>
+          <t>16:30:19</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2400,11 +2400,11 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>سارا محمدی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>18:00:19</t>
+          <t>16:30:44</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2435,11 +2435,11 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>امیر جعفری</t>
+          <t>رضا کریمی</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>18:00:39</t>
+          <t>17:30:28</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2470,11 +2470,11 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>امیر جعفری</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>18:00:44</t>
+          <t>18:00:39</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>02:00:10</t>
+          <t>00:30:10</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>02:00:57</t>
+          <t>00:30:57</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>10:00:16</t>
+          <t>09:00:16</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>10:00:51</t>
+          <t>09:00:51</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2715,11 +2715,11 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>علی رضایی</t>
+          <t>نیما احمدی</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>16:00:42</t>
+          <t>16:30:08</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>17:15:08</t>
+          <t>16:30:20</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -2785,11 +2785,11 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>نیما احمدی</t>
+          <t>علی رضایی</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>17:15:20</t>
+          <t>17:30:42</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>01:00:35</t>
+          <t>00:30:35</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>02:00:46</t>
+          <t>00:30:46</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>10:00:38</t>
+          <t>08:30:38</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>10:00:44</t>
+          <t>08:50:44</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2995,11 +2995,11 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>علی رضایی</t>
+          <t>سارا محمدی</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>16:00:05</t>
+          <t>16:30:27</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3030,11 +3030,11 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>امیر جعفری</t>
+          <t>مریم حسینی</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>16:00:59</t>
+          <t>16:30:33</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3065,11 +3065,11 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>سارا محمدی</t>
+          <t>علی رضایی</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>18:00:27</t>
+          <t>17:30:05</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>ورود</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3100,34 +3100,104 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>امیر جعفری</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>1405/08/07</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:30:59</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>خروج</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>چهره</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>DEV-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>سارا محمدی</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>1405/08/08</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>02:00:14</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>01:00:14</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>خروج</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>چهره</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>چهره</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>DEV-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>مریم حسینی</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>1405/08/08</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>01:20:48</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>خروج</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>چهره</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>DEV-01</t>
         </is>
@@ -3358,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3404,7 +3474,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/08/01 جمعه</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -3414,7 +3484,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>صبح عادی</t>
+          <t>صبح عادی (حضور الزامی 08:30)</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -3429,14 +3499,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>انحراف‌ها در حد چند دقیقه</t>
+          <t>خروج 17:35؛ 5 دقیقه اضافه‌کار در انتظار تأیید</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/08/01 جمعه</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -3461,14 +3531,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>خروج 02:10 تاریخ 08/02 جزو روز کاری 08/01</t>
+          <t>خروج 00:32 تاریخ 08/02 جزو روز کاری 08/01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/08/01 جمعه</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -3478,7 +3548,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>دوشیفت کامل</t>
+          <t>دوشیفت، استراحت 15:00 تا 17:02</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -3493,14 +3563,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>استراحت 2:05</t>
+          <t>استراحت 2:02؛ کسر کار 0:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/08/01 جمعه</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -3510,7 +3580,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>دو ورود پشت سر هم (10:00 و 10:10)</t>
+          <t>دو ورود پشت سر هم (08:30 و 08:40)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3525,14 +3595,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ورود زودتر یعنی 10:00 مبنا</t>
+          <t>ورود زودتر یعنی 08:30 مبنا</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/08/01 جمعه</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -3542,7 +3612,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>دو خروج پشت سر هم (01:50 و 02:05)</t>
+          <t>دو خروج پشت سر هم (00:20 و 00:35)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3557,14 +3627,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>خروج دیرتر یعنی 02:05 مبنا</t>
+          <t>خروج دیرتر یعنی 00:35 مبنا؛ 5 دقیقه اضافه‌کار در انتظار تأیید</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>1405/08/01</t>
+          <t>1405/08/01 جمعه</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -3579,7 +3649,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>بدون تردد</t>
+          <t>تعیین‌نشده</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -3596,7 +3666,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>1405/08/02</t>
+          <t>1405/08/02 شنبه</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -3606,7 +3676,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>فقط ورود صبح</t>
+          <t>فقط ورود صبح (09:05، داخل تلورانس)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3616,19 +3686,19 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>خروج صبح = 13:00 (بدبینانه)</t>
+          <t>خروج صبح = 12:00 (بدبینانه)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>توضیح بدبینانه برای پرسنل</t>
+          <t>تأخیر صفر؛ توضیح بدبینانه برای پرسنل</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>1405/08/02</t>
+          <t>1405/08/02 شنبه</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -3638,7 +3708,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>فقط خروج شب (02:00 تاریخ 08/03)</t>
+          <t>فقط خروج شب (00:30 تاریخ 08/03)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3660,7 +3730,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>1405/08/02</t>
+          <t>1405/08/02 شنبه</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -3680,7 +3750,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>خروج صبح 16:00 و ورود عصر 18:00 (استراحت استاندارد)</t>
+          <t>استراحت 2:00 کسر می‌شود؛ ساعت استراحت نامشخص</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3692,7 +3762,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>1405/08/02</t>
+          <t>1405/08/02 شنبه</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -3702,7 +3772,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>خروج قبل از استراحت جا افتاده</t>
+          <t>خروج برای استراحت جا افتاده</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3720,7 +3790,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>1405/08/02</t>
+          <t>1405/08/02 شنبه</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -3730,7 +3800,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>عصر با تأخیر 10 دقیقه</t>
+          <t>عصر با تأخیر 10 دقیقه (16:40)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3745,14 +3815,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>تأخیر ورود عصر 0:10</t>
+          <t>عصر تلورانس ندارد؛ تأخیر 0:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1405/08/03</t>
+          <t>1405/08/03 یکشنبه</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -3772,7 +3842,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ورود صبح = 13:00 (بدبینانه)</t>
+          <t>ورود صبح = 12:00 (بدبینانه)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3784,7 +3854,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>1405/08/03</t>
+          <t>1405/08/03 یکشنبه</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -3816,7 +3886,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>1405/08/03</t>
+          <t>1405/08/03 یکشنبه</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -3844,7 +3914,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1405/08/03</t>
+          <t>1405/08/03 یکشنبه</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -3876,7 +3946,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1405/08/03</t>
+          <t>1405/08/03 یکشنبه</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -3886,7 +3956,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>خروج 16:00 و ورود اشتباهی 16:01</t>
+          <t>خروج 17:30 و ورود اشتباهی 17:31</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3908,7 +3978,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1405/08/03</t>
+          <t>1405/08/03 یکشنبه</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -3918,7 +3988,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>ورود صبح با 90 دقیقه تأخیر</t>
+          <t>ورود صبح 09:20 (بیرون از تلورانس)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3933,14 +4003,14 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>تأخیر ورود صبح 1:30</t>
+          <t>تأخیر 0:20 (کامل، از 09:00)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1405/08/04</t>
+          <t>1405/08/04 دوشنبه</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -3950,7 +4020,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>تعجیل خروج صبح (14:30)</t>
+          <t>ورود 09:14 داخل تلورانس، خروج زود 16:00</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3965,14 +4035,14 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>کسر کار 1:30</t>
+          <t>تأخیر صفر؛ تعجیل خروج 1:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>1405/08/04</t>
+          <t>1405/08/04 دوشنبه</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -3982,7 +4052,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>اضافه‌کار عصر (خروج 03:15)</t>
+          <t>خروج 01:30 (یک ساعت بعد از پایان)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -3997,14 +4067,14 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>اضافه‌کار 1:15</t>
+          <t>1:00 اضافه‌کار در انتظار تأیید</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>1405/08/04</t>
+          <t>1405/08/04 دوشنبه</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -4014,7 +4084,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>استراحت طولانی (16:00 تا 19:00)</t>
+          <t>استراحت طولانی (15:00 تا 18:00)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -4036,7 +4106,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1405/08/04</t>
+          <t>1405/08/04 دوشنبه</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -4046,7 +4116,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>ورود عصر زودتر از موعد (17:00)</t>
+          <t>ورود عصر زودتر از موعد (16:00)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4061,14 +4131,14 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>زودآمدن اضافه‌کار حساب نمی‌شود مگر تنظیمات اجازه دهد</t>
+          <t>زودآمدن اضافه‌کار حساب نمی‌شود</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>1405/08/04</t>
+          <t>1405/08/04 دوشنبه</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -4083,7 +4153,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>تک‌شیفت صبح؟</t>
+          <t>نیاز به بررسی</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -4093,14 +4163,14 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>نیاز به بررسی</t>
+          <t>مدیر بررسی می‌کند</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>1405/08/05</t>
+          <t>1405/08/05 سه‌شنبه</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -4115,7 +4185,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>بدون تردد</t>
+          <t>تعیین‌نشده</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -4132,7 +4202,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>1405/08/05</t>
+          <t>1405/08/05 سه‌شنبه</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -4164,7 +4234,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>1405/08/05</t>
+          <t>1405/08/05 سه‌شنبه</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -4174,7 +4244,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>دوشیفت کامل</t>
+          <t>دوشیفت، استراحت 16:00 تا 18:00</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -4187,12 +4257,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>ساعت استراحت برای هر نفر متفاوت است و مشکلی نیست</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>1405/08/06</t>
+          <t>1405/08/06 چهارشنبه</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -4202,7 +4276,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>خروج و ورود 17:15 پشت سر هم، بعد خروج شب</t>
+          <t>خروج و ورود 16:30 پشت سر هم، بعد خروج شب</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -4217,14 +4291,14 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>دو پانچ نزدیک یکی شدند؛ ورود عصر 17:15</t>
+          <t>دو پانچ نزدیک یکی شدند؛ ورود عصر 16:30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>1405/08/06</t>
+          <t>1405/08/06 چهارشنبه</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -4234,7 +4308,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>دوشیفت کامل</t>
+          <t>دوشیفت، استراحت 16:00 تا 18:00</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -4252,35 +4326,131 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>1405/08/07</t>
+          <t>1405/08/07 پنجشنبه</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>صبح پنجشنبه (حضور الزامی 08:30)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>تک‌شیفت صبح</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>1405/08/07 پنجشنبه</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>عصر عادی</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>پنجشنبه شب، خروج 01:00</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>تک‌شیفت عصر</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>پایان شیفت پنجشنبه 01:00 است؛ اضافه‌کار ندارد</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>این برگه فقط برای تست است و در خروجی دستگاه لازم نیست. ساعت‌ها بر اساس فرض صبح 10:00–16:00 و عصر 18:00–02:00 است.</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>1405/08/07 پنجشنبه</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>پنجشنبه شب، خروج 01:20</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>تک‌شیفت عصر</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>0:20 اضافه‌کار در انتظار تأیید مدیر</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>1405/08/07 پنجشنبه</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>ورود 08:50 (تلورانس 15 دقیقه)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>تک‌شیفت صبح</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>تأخیر 0:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>این برگه فقط برای تست است و در خروجی دستگاه لازم نیست. ساعت‌ها بر اساس برنامه‌ی پیش‌فرض پرامپت است (شنبه تا چهارشنبه حضور 09:00، پنجشنبه و جمعه 08:30، پنجره‌ها 06–12 / 12–21 / 21–06).</t>
         </is>
       </c>
     </row>
